--- a/diseases/d052/2026-2029.xlsx
+++ b/diseases/d052/2026-2029.xlsx
@@ -19845,6 +19845,154 @@
         </is>
       </c>
     </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>chikungunya</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>基孔肯雅热</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N126" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO126" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP126" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR126" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr"/>
+      <c r="AT126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU126" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV126" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA126" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB126" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC126" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19878,7 +20026,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -19961,7 +20109,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10">
@@ -19971,7 +20119,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d052/2026-2029.xlsx
+++ b/diseases/d052/2026-2029.xlsx
@@ -1061,9 +1061,6 @@
       <c r="O4" t="n">
         <v>11</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0.122116415132755</v>
       </c>
@@ -1357,9 +1354,6 @@
       <c r="O6" t="n">
         <v>3</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.05336427512592412</v>
       </c>
@@ -1753,9 +1747,6 @@
       <c r="O8" t="n">
         <v>2</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.02710540560393419</v>
       </c>
@@ -1901,9 +1892,6 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
@@ -3825,9 +3813,6 @@
       <c r="O22" t="n">
         <v>10</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0.1110149228479591</v>
       </c>
@@ -4121,9 +4106,6 @@
       <c r="O24" t="n">
         <v>1</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.01778809170864137</v>
       </c>
@@ -4517,9 +4499,6 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
@@ -4665,9 +4644,6 @@
       <c r="O27" t="n">
         <v>1</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0.001937969923792046</v>
       </c>
@@ -6441,9 +6417,6 @@
       <c r="O39" t="n">
         <v>10</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0.1110149228479591</v>
       </c>
@@ -6737,9 +6710,6 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
@@ -7133,9 +7103,6 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
@@ -7281,9 +7248,6 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
@@ -8761,9 +8725,6 @@
       <c r="O54" t="n">
         <v>5</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.01836405909759895</v>
       </c>
@@ -8909,9 +8870,6 @@
       <c r="O55" t="n">
         <v>25238</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>11.817608580009</v>
       </c>
@@ -9057,9 +9015,6 @@
       <c r="O56" t="n">
         <v>9</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.09991343056316315</v>
       </c>
@@ -9353,9 +9308,6 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
@@ -9749,9 +9701,6 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
@@ -9897,9 +9846,6 @@
       <c r="O61" t="n">
         <v>1</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0.001937969923792046</v>
       </c>
@@ -10045,9 +9991,6 @@
       <c r="O62" t="n">
         <v>1</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.004345692446436896</v>
       </c>
@@ -11377,9 +11320,6 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
@@ -11525,9 +11465,6 @@
       <c r="O72" t="n">
         <v>21823</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>10.2185463206885</v>
       </c>
@@ -11673,9 +11610,6 @@
       <c r="O73" t="n">
         <v>3</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0.03330447685438772</v>
       </c>
@@ -11969,9 +11903,6 @@
       <c r="O75" t="n">
         <v>1</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0.01778809170864137</v>
       </c>
@@ -12365,9 +12296,6 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
@@ -12513,9 +12441,6 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
@@ -12661,9 +12586,6 @@
       <c r="O79" t="n">
         <v>1</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0.004345692446436896</v>
       </c>
@@ -14289,9 +14211,6 @@
       <c r="O90" t="n">
         <v>0</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0</v>
       </c>
@@ -14437,9 +14356,6 @@
       <c r="O91" t="n">
         <v>13282</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>6.219251809163939</v>
       </c>
@@ -14733,9 +14649,6 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
@@ -15129,9 +15042,6 @@
       <c r="O95" t="n">
         <v>0</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0</v>
       </c>
@@ -15277,9 +15187,6 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
@@ -15425,9 +15332,6 @@
       <c r="O97" t="n">
         <v>1</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0.004345692446436896</v>
       </c>
@@ -15573,9 +15477,6 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
@@ -15721,9 +15622,6 @@
       <c r="O99" t="n">
         <v>0</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0</v>
       </c>
@@ -15869,9 +15767,6 @@
       <c r="O100" t="n">
         <v>1</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -16017,9 +15912,6 @@
       <c r="O101" t="n">
         <v>1</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -16165,9 +16057,6 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0</v>
       </c>
@@ -16313,9 +16202,6 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
@@ -16461,9 +16347,6 @@
       <c r="O104" t="n">
         <v>0</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
@@ -16609,9 +16492,6 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0</v>
       </c>
@@ -16757,9 +16637,6 @@
       <c r="O106" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0</v>
       </c>
@@ -16905,9 +16782,6 @@
       <c r="O107" t="n">
         <v>8040</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>3.764702947272856</v>
       </c>
@@ -17053,9 +16927,6 @@
       <c r="O108" t="n">
         <v>1</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0.01778809170864137</v>
       </c>
@@ -17449,9 +17320,6 @@
       <c r="O110" t="n">
         <v>3</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.005813909771376137</v>
       </c>
@@ -17597,9 +17465,6 @@
       <c r="O111" t="n">
         <v>3</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0.01303707733931069</v>
       </c>
@@ -17745,9 +17610,6 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0</v>
       </c>
@@ -17893,9 +17755,6 @@
       <c r="O113" t="n">
         <v>1</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -18041,9 +17900,6 @@
       <c r="O114" t="n">
         <v>0</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0</v>
       </c>
@@ -18189,9 +18045,6 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
@@ -18337,9 +18190,6 @@
       <c r="O116" t="n">
         <v>0</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0</v>
       </c>
@@ -18485,9 +18335,6 @@
       <c r="O117" t="n">
         <v>0</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0</v>
       </c>
@@ -18633,9 +18480,6 @@
       <c r="O118" t="n">
         <v>0</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0</v>
       </c>
@@ -18781,9 +18625,6 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
@@ -18929,9 +18770,6 @@
       <c r="O120" t="n">
         <v>1</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -19077,9 +18915,6 @@
       <c r="O121" t="n">
         <v>0</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0</v>
       </c>
@@ -19225,9 +19060,6 @@
       <c r="O122" t="n">
         <v>11</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0.005150712987562365</v>
       </c>
@@ -19373,9 +19205,6 @@
       <c r="O123" t="n">
         <v>0</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0</v>
       </c>
@@ -19769,9 +19598,6 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0</v>
       </c>
@@ -19915,9 +19741,6 @@
         <v>0</v>
       </c>
       <c r="O126" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q126" t="n">
         <v>0</v>
       </c>
       <c r="R126" t="n">

--- a/diseases/d052/2026-2029.xlsx
+++ b/diseases/d052/2026-2029.xlsx
@@ -19699,12 +19699,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -19729,7 +19729,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -19738,13 +19738,13 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R126" t="n">
-        <v>0</v>
+        <v>0.004345692446436896</v>
       </c>
       <c r="S126" t="inlineStr">
         <is>
@@ -19777,40 +19777,185 @@
       </c>
       <c r="AV126" t="inlineStr">
         <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA126" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB126" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC126" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>chikungunya</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>基孔肯雅热</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP127" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR127" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr"/>
+      <c r="AT127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU127" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV127" t="inlineStr">
+        <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW126" t="inlineStr">
+      <c r="AW127" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX126" t="inlineStr">
+      <c r="AX127" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY126" t="inlineStr">
+      <c r="AY127" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ126" t="inlineStr">
+      <c r="AZ127" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA126" t="inlineStr">
+      <c r="BA127" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB126" t="inlineStr">
+      <c r="BB127" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC126" t="inlineStr">
+      <c r="BC127" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -19932,7 +20077,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10">
@@ -19942,7 +20087,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11">
@@ -19994,7 +20139,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>112099</v>
+        <v>112100</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d052/2026-2029.xlsx
+++ b/diseases/d052/2026-2029.xlsx
@@ -19593,13 +19593,13 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S125" t="inlineStr">
         <is>
@@ -19956,6 +19956,151 @@
         </is>
       </c>
       <c r="BC127" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>chikungunya</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>基孔肯雅热</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N128" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0</v>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO128" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP128" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR128" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS128" t="inlineStr"/>
+      <c r="AT128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU128" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV128" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA128" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB128" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC128" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -19994,7 +20139,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -20077,7 +20222,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10">
@@ -20087,7 +20232,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11">
@@ -20139,7 +20284,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>112100</v>
+        <v>112101</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d052/2026-2029.xlsx
+++ b/diseases/d052/2026-2029.xlsx
@@ -16883,12 +16883,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -16922,95 +16922,84 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>1</v>
+        <v>186</v>
       </c>
       <c r="O108" t="n">
-        <v>1</v>
+        <v>186</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.01316428235190607</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U108" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1185</t>
-        </is>
-      </c>
-      <c r="AA108" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ108" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS108" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1185</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR108" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS108" t="inlineStr"/>
       <c r="AT108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB108" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC108" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -17037,7 +17026,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -17086,98 +17075,23 @@
       <c r="O109" t="n">
         <v>1</v>
       </c>
+      <c r="R109" t="n">
+        <v>0.01778809170864137</v>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U109" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1185</t>
         </is>
       </c>
-      <c r="V109" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1185</t>
-        </is>
-      </c>
-      <c r="W109" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X109" t="inlineStr">
-        <is>
-          <t>Chikungunya</t>
-        </is>
-      </c>
-      <c r="Y109" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD109" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE109" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF109" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG109" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH109" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI109" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ109" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK109" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1185.</t>
-        </is>
-      </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN109" t="b">
-        <v>1</v>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
@@ -17271,17 +17185,17 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -17315,81 +17229,170 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O110" t="n">
-        <v>3</v>
-      </c>
-      <c r="R110" t="n">
-        <v>0.005813909771376137</v>
-      </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1185</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1185</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X110" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD110" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE110" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF110" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG110" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1185.</t>
+        </is>
+      </c>
+      <c r="AM110" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN110" t="b">
+        <v>1</v>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR110" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS110" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ110" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS110" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1185</t>
+        </is>
+      </c>
       <c r="AT110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB110" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC110" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -17421,12 +17424,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -17466,7 +17469,7 @@
         <v>3</v>
       </c>
       <c r="R111" t="n">
-        <v>0.01303707733931069</v>
+        <v>0.005813909771376137</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
@@ -17499,42 +17502,42 @@
       </c>
       <c r="AV111" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB111" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC111" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -17566,12 +17569,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -17596,7 +17599,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -17605,13 +17608,13 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O112" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>0.01303707733931069</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -17644,42 +17647,42 @@
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB112" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC112" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -17711,12 +17714,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -17750,13 +17753,13 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
@@ -17789,42 +17792,42 @@
       </c>
       <c r="AV113" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB113" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC113" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -17856,12 +17859,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -17886,7 +17889,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -17895,13 +17898,13 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R114" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -17934,42 +17937,42 @@
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC114" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -18001,12 +18004,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -18079,42 +18082,42 @@
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -18146,12 +18149,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -18176,7 +18179,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -18224,42 +18227,42 @@
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -18291,12 +18294,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -18369,42 +18372,42 @@
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -18436,12 +18439,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -18466,7 +18469,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -18514,42 +18517,42 @@
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -18581,12 +18584,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -18659,42 +18662,42 @@
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -18726,12 +18729,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -18756,7 +18759,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -18765,13 +18768,13 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
@@ -18804,42 +18807,42 @@
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -18871,12 +18874,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -18901,22 +18904,22 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S121" t="inlineStr">
         <is>
@@ -18949,42 +18952,42 @@
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -19016,12 +19019,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -19055,13 +19058,13 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>0.005150712987562365</v>
+        <v>0</v>
       </c>
       <c r="S122" t="inlineStr">
         <is>
@@ -19094,42 +19097,42 @@
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -19161,12 +19164,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -19200,95 +19203,81 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O123" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>0.005150712987562365</v>
       </c>
       <c r="S123" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U123" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1185</t>
-        </is>
-      </c>
-      <c r="AA123" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ123" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS123" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1185</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR123" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr"/>
       <c r="AT123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -19315,7 +19304,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -19364,98 +19353,23 @@
       <c r="O124" t="n">
         <v>0</v>
       </c>
+      <c r="R124" t="n">
+        <v>0</v>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U124" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1185</t>
         </is>
       </c>
-      <c r="V124" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1185</t>
-        </is>
-      </c>
-      <c r="W124" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X124" t="inlineStr">
-        <is>
-          <t>Chikungunya</t>
-        </is>
-      </c>
-      <c r="Y124" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD124" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE124" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF124" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG124" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH124" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI124" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ124" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK124" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1185.</t>
-        </is>
-      </c>
-      <c r="AM124" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN124" t="b">
-        <v>1</v>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
@@ -19549,17 +19463,17 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -19593,81 +19507,170 @@
         </is>
       </c>
       <c r="N125" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1185</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1185</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD125" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF125" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG125" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1185.</t>
+        </is>
+      </c>
+      <c r="AM125" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN125" t="b">
         <v>1</v>
       </c>
-      <c r="O125" t="n">
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP125" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ125" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1185</t>
+        </is>
+      </c>
+      <c r="AT125" t="n">
         <v>1</v>
       </c>
-      <c r="R125" t="n">
-        <v>0.001937969923792046</v>
-      </c>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO125" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP125" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR125" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS125" t="inlineStr"/>
-      <c r="AT125" t="n">
-        <v>0</v>
-      </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -19699,12 +19702,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -19744,7 +19747,7 @@
         <v>1</v>
       </c>
       <c r="R126" t="n">
-        <v>0.004345692446436896</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S126" t="inlineStr">
         <is>
@@ -19777,42 +19780,42 @@
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -19844,12 +19847,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -19874,7 +19877,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -19883,13 +19886,13 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R127" t="n">
-        <v>0</v>
+        <v>0.004345692446436896</v>
       </c>
       <c r="S127" t="inlineStr">
         <is>
@@ -19922,42 +19925,42 @@
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -20019,7 +20022,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -20101,6 +20104,151 @@
         </is>
       </c>
       <c r="BC128" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>chikungunya</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>基孔肯雅热</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N129" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0</v>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO129" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP129" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR129" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS129" t="inlineStr"/>
+      <c r="AT129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU129" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV129" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA129" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB129" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC129" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -20222,7 +20370,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10">
@@ -20232,7 +20380,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11">
@@ -20284,7 +20432,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>112101</v>
+        <v>112287</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d052/2026-2029.xlsx
+++ b/diseases/d052/2026-2029.xlsx
@@ -19348,13 +19348,13 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R124" t="n">
-        <v>0</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
@@ -19507,10 +19507,10 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U125" t="inlineStr">
         <is>
@@ -20251,6 +20251,151 @@
       <c r="BC129" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>chikungunya</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>基孔肯雅热</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N130" t="n">
+        <v>2</v>
+      </c>
+      <c r="O130" t="n">
+        <v>2</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.0005730076265538771</v>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP130" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR130" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS130" t="inlineStr"/>
+      <c r="AT130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU130" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV130" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA130" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB130" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC130" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -20287,7 +20432,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -20370,7 +20515,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10">
@@ -20380,7 +20525,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11">
@@ -20432,7 +20577,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>112287</v>
+        <v>112290</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d052/2026-2029.xlsx
+++ b/diseases/d052/2026-2029.xlsx
@@ -14351,13 +14351,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>13282</v>
+        <v>13777</v>
       </c>
       <c r="O91" t="n">
-        <v>13282</v>
+        <v>13777</v>
       </c>
       <c r="R91" t="n">
-        <v>6.219251809163939</v>
+        <v>6.451033893604246</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -16777,13 +16777,13 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>8040</v>
+        <v>10364</v>
       </c>
       <c r="O107" t="n">
-        <v>8040</v>
+        <v>10364</v>
       </c>
       <c r="R107" t="n">
-        <v>3.764702947272856</v>
+        <v>4.852908127554214</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
@@ -19203,13 +19203,13 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>11</v>
+        <v>2432</v>
       </c>
       <c r="O123" t="n">
-        <v>11</v>
+        <v>2432</v>
       </c>
       <c r="R123" t="n">
-        <v>0.005150712987562365</v>
+        <v>1.138775816886516</v>
       </c>
       <c r="S123" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>112290</v>
+        <v>117530</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d052/2026-2029.xlsx
+++ b/diseases/d052/2026-2029.xlsx
@@ -14351,13 +14351,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>13777</v>
+        <v>13901</v>
       </c>
       <c r="O91" t="n">
-        <v>13777</v>
+        <v>13901</v>
       </c>
       <c r="R91" t="n">
-        <v>6.451033893604246</v>
+        <v>6.509096476373131</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -16777,13 +16777,13 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>10364</v>
+        <v>10988</v>
       </c>
       <c r="O107" t="n">
-        <v>10364</v>
+        <v>10988</v>
       </c>
       <c r="R107" t="n">
-        <v>4.852908127554214</v>
+        <v>5.14509402793957</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
@@ -19203,13 +19203,13 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>2432</v>
+        <v>4202</v>
       </c>
       <c r="O123" t="n">
-        <v>2432</v>
+        <v>4202</v>
       </c>
       <c r="R123" t="n">
-        <v>1.138775816886516</v>
+        <v>1.967572361248823</v>
       </c>
       <c r="S123" t="inlineStr">
         <is>
@@ -20396,6 +20396,151 @@
       <c r="BC130" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>chikungunya</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>基孔肯雅热</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N131" t="n">
+        <v>0</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0</v>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO131" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP131" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR131" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr"/>
+      <c r="AT131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU131" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV131" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA131" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB131" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC131" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -20432,7 +20577,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -20515,7 +20660,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10">
@@ -20525,7 +20670,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11">
@@ -20577,7 +20722,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>117530</v>
+        <v>120048</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d052/2026-2029.xlsx
+++ b/diseases/d052/2026-2029.xlsx
@@ -27668,12 +27668,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -27707,13 +27707,13 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O163" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R163" t="n">
-        <v>0.005813909771376137</v>
+        <v>0</v>
       </c>
       <c r="S163" t="inlineStr">
         <is>
@@ -27746,42 +27746,42 @@
       </c>
       <c r="AV163" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA163" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB163" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC163" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -27813,12 +27813,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -27858,7 +27858,7 @@
         <v>3</v>
       </c>
       <c r="R164" t="n">
-        <v>0.01303707733931069</v>
+        <v>0.005813909771376137</v>
       </c>
       <c r="S164" t="inlineStr">
         <is>
@@ -27891,42 +27891,42 @@
       </c>
       <c r="AV164" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA164" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB164" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC164" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -27958,12 +27958,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -27988,7 +27988,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
@@ -27997,13 +27997,13 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O165" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R165" t="n">
-        <v>0</v>
+        <v>0.01303707733931069</v>
       </c>
       <c r="S165" t="inlineStr">
         <is>
@@ -28036,42 +28036,42 @@
       </c>
       <c r="AV165" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA165" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB165" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC165" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -28103,12 +28103,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -28142,13 +28142,13 @@
         </is>
       </c>
       <c r="N166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R166" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S166" t="inlineStr">
         <is>
@@ -28181,42 +28181,42 @@
       </c>
       <c r="AV166" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA166" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB166" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC166" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -28248,12 +28248,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -28278,7 +28278,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
@@ -28287,93 +28287,81 @@
         </is>
       </c>
       <c r="N167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O167" t="n">
-        <v>0</v>
-      </c>
-      <c r="P167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R167" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S167" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA167" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO167" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ167" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS167" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHIKUNGUNYA; SER_SG_HIST_CHIKUNGUNYA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR167" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr"/>
       <c r="AT167" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA167" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB167" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC167" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -28400,7 +28388,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -28452,98 +28440,18 @@
       <c r="P168" t="n">
         <v>0</v>
       </c>
-      <c r="U168" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHIKUNGUNYA</t>
-        </is>
-      </c>
-      <c r="V168" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHIKUNGUNYA</t>
-        </is>
-      </c>
-      <c r="W168" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X168" t="inlineStr">
-        <is>
-          <t>Chikungunya</t>
-        </is>
-      </c>
-      <c r="Y168" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z168" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R168" t="n">
+        <v>0</v>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB168" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC168" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD168" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE168" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF168" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG168" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH168" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI168" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ168" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK168" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM168" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN168" t="b">
-        <v>1</v>
       </c>
       <c r="AO168" t="inlineStr">
         <is>
@@ -28637,17 +28545,17 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -28672,7 +28580,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
@@ -28686,76 +28594,168 @@
       <c r="O169" t="n">
         <v>0</v>
       </c>
-      <c r="R169" t="n">
-        <v>0</v>
-      </c>
-      <c r="S169" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P169" t="n">
+        <v>0</v>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X169" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD169" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE169" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF169" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG169" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH169" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI169" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ169" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM169" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN169" t="b">
+        <v>1</v>
       </c>
       <c r="AO169" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR169" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS169" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ169" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS169" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA; SER_SG_HIST_CHIKUNGUNYA</t>
+        </is>
+      </c>
       <c r="AT169" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU169" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV169" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA169" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB169" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC169" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -28787,12 +28787,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -28865,42 +28865,42 @@
       </c>
       <c r="AV170" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA170" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB170" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC170" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -28932,12 +28932,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -28962,7 +28962,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -28976,9 +28976,6 @@
       <c r="O171" t="n">
         <v>0</v>
       </c>
-      <c r="P171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>0</v>
       </c>
@@ -28987,77 +28984,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA171" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO171" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ171" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS171" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHIKUNGUNYA; SER_SG_HIST_CHIKUNGUNYA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR171" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS171" t="inlineStr"/>
       <c r="AT171" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU171" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV171" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA171" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB171" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC171" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -29084,7 +29072,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -29136,98 +29124,18 @@
       <c r="P172" t="n">
         <v>0</v>
       </c>
-      <c r="U172" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHIKUNGUNYA</t>
-        </is>
-      </c>
-      <c r="V172" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHIKUNGUNYA</t>
-        </is>
-      </c>
-      <c r="W172" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X172" t="inlineStr">
-        <is>
-          <t>Chikungunya</t>
-        </is>
-      </c>
-      <c r="Y172" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z172" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R172" t="n">
+        <v>0</v>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB172" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC172" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD172" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE172" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF172" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG172" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH172" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI172" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ172" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK172" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM172" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN172" t="b">
-        <v>1</v>
       </c>
       <c r="AO172" t="inlineStr">
         <is>
@@ -29321,17 +29229,17 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -29356,7 +29264,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -29370,76 +29278,168 @@
       <c r="O173" t="n">
         <v>0</v>
       </c>
-      <c r="R173" t="n">
-        <v>0</v>
-      </c>
-      <c r="S173" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P173" t="n">
+        <v>0</v>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X173" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD173" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE173" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF173" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG173" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH173" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI173" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ173" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK173" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM173" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN173" t="b">
+        <v>1</v>
       </c>
       <c r="AO173" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR173" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS173" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ173" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS173" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA; SER_SG_HIST_CHIKUNGUNYA</t>
+        </is>
+      </c>
       <c r="AT173" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA173" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB173" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC173" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -29471,12 +29471,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -29549,42 +29549,42 @@
       </c>
       <c r="AV174" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA174" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB174" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC174" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -29616,12 +29616,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -29646,7 +29646,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -29660,9 +29660,6 @@
       <c r="O175" t="n">
         <v>0</v>
       </c>
-      <c r="P175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>0</v>
       </c>
@@ -29671,77 +29668,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA175" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO175" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ175" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS175" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHIKUNGUNYA; SER_SG_HIST_CHIKUNGUNYA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR175" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS175" t="inlineStr"/>
       <c r="AT175" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV175" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA175" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB175" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC175" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -29768,7 +29756,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -29820,98 +29808,18 @@
       <c r="P176" t="n">
         <v>0</v>
       </c>
-      <c r="U176" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHIKUNGUNYA</t>
-        </is>
-      </c>
-      <c r="V176" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHIKUNGUNYA</t>
-        </is>
-      </c>
-      <c r="W176" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X176" t="inlineStr">
-        <is>
-          <t>Chikungunya</t>
-        </is>
-      </c>
-      <c r="Y176" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z176" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R176" t="n">
+        <v>0</v>
+      </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB176" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC176" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD176" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE176" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF176" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG176" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH176" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI176" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ176" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK176" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM176" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN176" t="b">
-        <v>1</v>
       </c>
       <c r="AO176" t="inlineStr">
         <is>
@@ -30005,17 +29913,17 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -30040,7 +29948,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
@@ -30054,76 +29962,168 @@
       <c r="O177" t="n">
         <v>0</v>
       </c>
-      <c r="R177" t="n">
-        <v>0</v>
-      </c>
-      <c r="S177" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P177" t="n">
+        <v>0</v>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA</t>
+        </is>
+      </c>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA</t>
+        </is>
+      </c>
+      <c r="W177" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X177" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB177" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD177" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE177" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF177" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG177" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH177" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI177" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ177" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK177" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM177" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN177" t="b">
+        <v>1</v>
       </c>
       <c r="AO177" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR177" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS177" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ177" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS177" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA; SER_SG_HIST_CHIKUNGUNYA</t>
+        </is>
+      </c>
       <c r="AT177" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV177" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA177" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB177" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC177" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -30155,12 +30155,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -30233,42 +30233,42 @@
       </c>
       <c r="AV178" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA178" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB178" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC178" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -30300,12 +30300,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -30330,7 +30330,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -30339,13 +30339,13 @@
         </is>
       </c>
       <c r="N179" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O179" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R179" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S179" t="inlineStr">
         <is>
@@ -30378,42 +30378,42 @@
       </c>
       <c r="AV179" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA179" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB179" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC179" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -30445,12 +30445,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -30484,93 +30484,81 @@
         </is>
       </c>
       <c r="N180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O180" t="n">
-        <v>0</v>
-      </c>
-      <c r="P180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R180" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S180" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA180" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO180" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ180" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS180" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHIKUNGUNYA; SER_SG_HIST_CHIKUNGUNYA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR180" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS180" t="inlineStr"/>
       <c r="AT180" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU180" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV180" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA180" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB180" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC180" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -30597,7 +30585,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -30649,98 +30637,18 @@
       <c r="P181" t="n">
         <v>0</v>
       </c>
-      <c r="U181" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHIKUNGUNYA</t>
-        </is>
-      </c>
-      <c r="V181" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHIKUNGUNYA</t>
-        </is>
-      </c>
-      <c r="W181" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X181" t="inlineStr">
-        <is>
-          <t>Chikungunya</t>
-        </is>
-      </c>
-      <c r="Y181" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z181" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R181" t="n">
+        <v>0</v>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB181" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC181" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD181" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE181" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF181" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG181" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH181" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI181" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ181" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK181" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM181" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN181" t="b">
-        <v>1</v>
       </c>
       <c r="AO181" t="inlineStr">
         <is>
@@ -30834,17 +30742,17 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -30869,12 +30777,12 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N182" t="n">
@@ -30883,76 +30791,168 @@
       <c r="O182" t="n">
         <v>0</v>
       </c>
-      <c r="R182" t="n">
-        <v>0</v>
-      </c>
-      <c r="S182" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P182" t="n">
+        <v>0</v>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA</t>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA</t>
+        </is>
+      </c>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X182" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z182" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB182" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD182" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE182" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF182" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG182" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH182" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI182" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ182" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK182" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM182" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN182" t="b">
+        <v>1</v>
       </c>
       <c r="AO182" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP182" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR182" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS182" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ182" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS182" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA; SER_SG_HIST_CHIKUNGUNYA</t>
+        </is>
+      </c>
       <c r="AT182" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU182" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV182" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA182" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB182" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC182" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -30984,12 +30984,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -31023,13 +31023,13 @@
         </is>
       </c>
       <c r="N183" t="n">
-        <v>4202</v>
+        <v>0</v>
       </c>
       <c r="O183" t="n">
-        <v>4202</v>
+        <v>0</v>
       </c>
       <c r="R183" t="n">
-        <v>1.967572361248823</v>
+        <v>0</v>
       </c>
       <c r="S183" t="inlineStr">
         <is>
@@ -31062,42 +31062,42 @@
       </c>
       <c r="AV183" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA183" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB183" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC183" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -31129,12 +31129,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -31168,95 +31168,81 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>1</v>
+        <v>4202</v>
       </c>
       <c r="O184" t="n">
-        <v>1</v>
+        <v>4202</v>
       </c>
       <c r="R184" t="n">
-        <v>0.01778809170864137</v>
+        <v>1.967572361248823</v>
       </c>
       <c r="S184" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U184" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1185</t>
-        </is>
-      </c>
-      <c r="AA184" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO184" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ184" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS184" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1185</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR184" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS184" t="inlineStr"/>
       <c r="AT184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV184" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA184" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB184" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC184" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -31283,7 +31269,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -31332,98 +31318,23 @@
       <c r="O185" t="n">
         <v>1</v>
       </c>
+      <c r="R185" t="n">
+        <v>0.01778809170864137</v>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U185" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1185</t>
         </is>
       </c>
-      <c r="V185" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1185</t>
-        </is>
-      </c>
-      <c r="W185" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X185" t="inlineStr">
-        <is>
-          <t>Chikungunya</t>
-        </is>
-      </c>
-      <c r="Y185" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z185" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA185" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB185" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC185" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD185" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE185" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF185" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG185" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH185" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI185" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ185" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK185" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1185.</t>
-        </is>
-      </c>
-      <c r="AM185" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN185" t="b">
-        <v>1</v>
       </c>
       <c r="AO185" t="inlineStr">
         <is>
@@ -31517,17 +31428,17 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -31566,76 +31477,165 @@
       <c r="O186" t="n">
         <v>1</v>
       </c>
-      <c r="R186" t="n">
-        <v>0.001937969923792046</v>
-      </c>
-      <c r="S186" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1185</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1185</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X186" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB186" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD186" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE186" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF186" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG186" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH186" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI186" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ186" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK186" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1185.</t>
+        </is>
+      </c>
+      <c r="AM186" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN186" t="b">
+        <v>1</v>
       </c>
       <c r="AO186" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP186" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR186" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS186" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ186" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS186" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1185</t>
+        </is>
+      </c>
       <c r="AT186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU186" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV186" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA186" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB186" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC186" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -31667,12 +31667,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -31712,7 +31712,7 @@
         <v>1</v>
       </c>
       <c r="R187" t="n">
-        <v>0.004345692446436896</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S187" t="inlineStr">
         <is>
@@ -31745,42 +31745,42 @@
       </c>
       <c r="AV187" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA187" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB187" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC187" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -31812,12 +31812,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -31842,7 +31842,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -31851,13 +31851,13 @@
         </is>
       </c>
       <c r="N188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R188" t="n">
-        <v>0</v>
+        <v>0.004345692446436896</v>
       </c>
       <c r="S188" t="inlineStr">
         <is>
@@ -31890,42 +31890,42 @@
       </c>
       <c r="AV188" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA188" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB188" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC188" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -31957,12 +31957,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -32001,9 +32001,6 @@
       <c r="O189" t="n">
         <v>0</v>
       </c>
-      <c r="P189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>0</v>
       </c>
@@ -32012,77 +32009,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA189" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO189" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP189" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ189" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS189" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHIKUNGUNYA; SER_SG_HIST_CHIKUNGUNYA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR189" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS189" t="inlineStr"/>
       <c r="AT189" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU189" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV189" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA189" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB189" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC189" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -32109,7 +32097,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -32161,98 +32149,18 @@
       <c r="P190" t="n">
         <v>0</v>
       </c>
-      <c r="U190" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHIKUNGUNYA</t>
-        </is>
-      </c>
-      <c r="V190" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHIKUNGUNYA</t>
-        </is>
-      </c>
-      <c r="W190" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X190" t="inlineStr">
-        <is>
-          <t>Chikungunya</t>
-        </is>
-      </c>
-      <c r="Y190" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z190" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R190" t="n">
+        <v>0</v>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB190" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC190" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD190" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE190" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF190" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG190" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH190" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI190" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ190" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK190" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM190" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN190" t="b">
-        <v>1</v>
       </c>
       <c r="AO190" t="inlineStr">
         <is>
@@ -32346,17 +32254,17 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -32381,7 +32289,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -32395,76 +32303,168 @@
       <c r="O191" t="n">
         <v>0</v>
       </c>
-      <c r="R191" t="n">
-        <v>0</v>
-      </c>
-      <c r="S191" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P191" t="n">
+        <v>0</v>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA</t>
+        </is>
+      </c>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA</t>
+        </is>
+      </c>
+      <c r="W191" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X191" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="Y191" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z191" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB191" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC191" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD191" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE191" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF191" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG191" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH191" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI191" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ191" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK191" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM191" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN191" t="b">
+        <v>1</v>
       </c>
       <c r="AO191" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR191" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS191" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ191" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS191" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA; SER_SG_HIST_CHIKUNGUNYA</t>
+        </is>
+      </c>
       <c r="AT191" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU191" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV191" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA191" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB191" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC191" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -32496,12 +32496,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -32540,9 +32540,6 @@
       <c r="O192" t="n">
         <v>0</v>
       </c>
-      <c r="P192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>0</v>
       </c>
@@ -32551,77 +32548,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA192" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO192" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP192" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ192" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS192" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHIKUNGUNYA; SER_SG_HIST_CHIKUNGUNYA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR192" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS192" t="inlineStr"/>
       <c r="AT192" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU192" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV192" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA192" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB192" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC192" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -32648,7 +32636,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -32700,98 +32688,18 @@
       <c r="P193" t="n">
         <v>0</v>
       </c>
-      <c r="U193" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHIKUNGUNYA</t>
-        </is>
-      </c>
-      <c r="V193" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHIKUNGUNYA</t>
-        </is>
-      </c>
-      <c r="W193" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X193" t="inlineStr">
-        <is>
-          <t>Chikungunya</t>
-        </is>
-      </c>
-      <c r="Y193" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z193" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R193" t="n">
+        <v>0</v>
+      </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB193" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC193" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD193" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE193" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF193" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG193" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH193" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI193" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ193" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK193" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM193" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN193" t="b">
-        <v>1</v>
       </c>
       <c r="AO193" t="inlineStr">
         <is>
@@ -32885,17 +32793,17 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -32920,7 +32828,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
@@ -32929,81 +32837,173 @@
         </is>
       </c>
       <c r="N194" t="n">
+        <v>0</v>
+      </c>
+      <c r="O194" t="n">
+        <v>0</v>
+      </c>
+      <c r="P194" t="n">
+        <v>0</v>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA</t>
+        </is>
+      </c>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA</t>
+        </is>
+      </c>
+      <c r="W194" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X194" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="Y194" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB194" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD194" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE194" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF194" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG194" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH194" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI194" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ194" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK194" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM194" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN194" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO194" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP194" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ194" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS194" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA; SER_SG_HIST_CHIKUNGUNYA</t>
+        </is>
+      </c>
+      <c r="AT194" t="n">
         <v>2</v>
       </c>
-      <c r="O194" t="n">
-        <v>2</v>
-      </c>
-      <c r="R194" t="n">
-        <v>0.0005730076265538771</v>
-      </c>
-      <c r="S194" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO194" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP194" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR194" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS194" t="inlineStr"/>
-      <c r="AT194" t="n">
-        <v>0</v>
-      </c>
       <c r="AU194" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV194" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA194" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB194" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC194" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -33035,12 +33035,12 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -33065,7 +33065,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -33074,13 +33074,13 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O195" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R195" t="n">
-        <v>0</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S195" t="inlineStr">
         <is>
@@ -33113,42 +33113,42 @@
       </c>
       <c r="AV195" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA195" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB195" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC195" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -33180,12 +33180,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -33224,9 +33224,6 @@
       <c r="O196" t="n">
         <v>0</v>
       </c>
-      <c r="P196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>0</v>
       </c>
@@ -33235,77 +33232,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA196" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO196" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP196" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ196" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS196" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHIKUNGUNYA; SER_SG_HIST_CHIKUNGUNYA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR196" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS196" t="inlineStr"/>
       <c r="AT196" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU196" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV196" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA196" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB196" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC196" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -33332,7 +33320,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -33384,98 +33372,18 @@
       <c r="P197" t="n">
         <v>0</v>
       </c>
-      <c r="U197" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHIKUNGUNYA</t>
-        </is>
-      </c>
-      <c r="V197" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHIKUNGUNYA</t>
-        </is>
-      </c>
-      <c r="W197" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X197" t="inlineStr">
-        <is>
-          <t>Chikungunya</t>
-        </is>
-      </c>
-      <c r="Y197" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z197" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R197" t="n">
+        <v>0</v>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB197" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC197" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD197" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE197" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF197" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG197" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH197" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI197" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ197" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK197" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM197" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN197" t="b">
-        <v>1</v>
       </c>
       <c r="AO197" t="inlineStr">
         <is>
@@ -33569,123 +33477,360 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>基孔肯雅热</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N198" t="n">
+        <v>0</v>
+      </c>
+      <c r="O198" t="n">
+        <v>0</v>
+      </c>
+      <c r="P198" t="n">
+        <v>0</v>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA</t>
+        </is>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA</t>
+        </is>
+      </c>
+      <c r="W198" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X198" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="Y198" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z198" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB198" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC198" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD198" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE198" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF198" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG198" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH198" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI198" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ198" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK198" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM198" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN198" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO198" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP198" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ198" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS198" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHIKUNGUNYA; SER_SG_HIST_CHIKUNGUNYA</t>
+        </is>
+      </c>
+      <c r="AT198" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU198" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV198" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW198" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX198" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY198" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA198" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB198" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC198" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>chikungunya</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F198" t="inlineStr">
+      <c r="F199" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G198" t="inlineStr">
+      <c r="G199" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>D052</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>Chikungunya</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr">
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
         <is>
           <t>基孔肯雅热</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr">
+      <c r="K199" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L198" t="inlineStr">
+      <c r="L199" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="M198" t="inlineStr">
+      <c r="M199" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="N198" t="n">
+      <c r="N199" t="n">
         <v>1</v>
       </c>
-      <c r="O198" t="n">
+      <c r="O199" t="n">
         <v>1</v>
       </c>
-      <c r="R198" t="n">
+      <c r="R199" t="n">
         <v>0.0002865038132769385</v>
       </c>
-      <c r="S198" t="inlineStr">
+      <c r="S199" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO198" t="inlineStr">
+      <c r="AO199" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP198" t="inlineStr">
+      <c r="AP199" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR198" t="inlineStr">
+      <c r="AR199" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS198" t="inlineStr"/>
-      <c r="AT198" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU198" t="inlineStr">
+      <c r="AS199" t="inlineStr"/>
+      <c r="AT199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU199" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV198" t="inlineStr">
+      <c r="AV199" t="inlineStr">
         <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW198" t="inlineStr">
+      <c r="AW199" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX198" t="inlineStr">
+      <c r="AX199" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY198" t="inlineStr">
+      <c r="AY199" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ198" t="inlineStr">
+      <c r="AZ199" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA198" t="inlineStr">
+      <c r="BA199" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB198" t="inlineStr">
+      <c r="BB199" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC198" t="inlineStr">
+      <c r="BC199" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -33807,7 +33952,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="10">
@@ -33817,7 +33962,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d052/2026-2029.xlsx
+++ b/diseases/d052/2026-2029.xlsx
@@ -1379,7 +1379,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -1387,17 +1387,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS6" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1185</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -1613,7 +1618,7 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -1621,17 +1626,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1185</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
@@ -5707,7 +5717,7 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
@@ -5715,17 +5725,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS32" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1185</t>
         </is>
       </c>
       <c r="AT32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
@@ -5941,7 +5956,7 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
@@ -5949,17 +5964,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS33" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1185</t>
         </is>
       </c>
       <c r="AT33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
@@ -9887,7 +9907,7 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ57" t="inlineStr">
@@ -9895,17 +9915,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS57" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1185</t>
         </is>
       </c>
       <c r="AT57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
@@ -10121,7 +10146,7 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ58" t="inlineStr">
@@ -10129,17 +10154,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS58" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1185</t>
         </is>
       </c>
       <c r="AT58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
@@ -14455,7 +14485,7 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ84" t="inlineStr">
@@ -14463,17 +14493,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS84" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1185</t>
         </is>
       </c>
       <c r="AT84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV84" t="inlineStr">
@@ -14689,7 +14724,7 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ85" t="inlineStr">
@@ -14697,17 +14732,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS85" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1185</t>
         </is>
       </c>
       <c r="AT85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV85" t="inlineStr">
@@ -18626,7 +18666,7 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ109" t="inlineStr">
@@ -18634,17 +18674,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR109" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS109" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1185</t>
         </is>
       </c>
       <c r="AT109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
@@ -18860,7 +18905,7 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ110" t="inlineStr">
@@ -18868,17 +18913,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS110" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1185</t>
         </is>
       </c>
       <c r="AT110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
@@ -23342,7 +23392,7 @@
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ137" t="inlineStr">
@@ -23350,17 +23400,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR137" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS137" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1185</t>
         </is>
       </c>
       <c r="AT137" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
@@ -23576,7 +23631,7 @@
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ138" t="inlineStr">
@@ -23584,17 +23639,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR138" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS138" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1185</t>
         </is>
       </c>
       <c r="AT138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV138" t="inlineStr">
@@ -27344,7 +27404,7 @@
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ161" t="inlineStr">
@@ -27352,17 +27412,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR161" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS161" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1185</t>
         </is>
       </c>
       <c r="AT161" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV161" t="inlineStr">
@@ -27578,7 +27643,7 @@
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ162" t="inlineStr">
@@ -27586,17 +27651,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR162" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS162" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1185</t>
         </is>
       </c>
       <c r="AT162" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV162" t="inlineStr">
@@ -31343,7 +31413,7 @@
       </c>
       <c r="AP185" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ185" t="inlineStr">
@@ -31351,17 +31421,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR185" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS185" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1185</t>
         </is>
       </c>
       <c r="AT185" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU185" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV185" t="inlineStr">
@@ -31577,7 +31652,7 @@
       </c>
       <c r="AP186" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ186" t="inlineStr">
@@ -31585,17 +31660,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR186" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS186" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1185</t>
         </is>
       </c>
       <c r="AT186" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU186" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV186" t="inlineStr">

--- a/diseases/d052/2026-2029.xlsx
+++ b/diseases/d052/2026-2029.xlsx
@@ -27933,13 +27933,13 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O165" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R165" t="n">
-        <v>0.01469124727807916</v>
+        <v>0.01836405909759895</v>
       </c>
       <c r="S165" t="inlineStr">
         <is>
@@ -37885,7 +37885,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>122741</v>
+        <v>122742</v>
       </c>
     </row>
     <row r="16">
